--- a/03_IE_tasks/data/related/outcomes_endpoints/Enpoints_gencturkRodentTestsDepression2024.xlsx
+++ b/03_IE_tasks/data/related/outcomes_endpoints/Enpoints_gencturkRodentTestsDepression2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sdoneva/Documents/Work/In Progress/PhD/PhD Projects/In Progress/Preclinical_Pipeline/03_IE_tasks/data/related/outcomes_endpoints/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED4AACE-33D4-E54D-A19C-09A81E37BA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5FBCDA7-59C9-B346-ACEA-06A7A7C13F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="1540" windowWidth="27640" windowHeight="16940" xr2:uid="{BC0DECDA-AED3-C249-929C-C34F56BC4720}"/>
+    <workbookView xWindow="42280" yWindow="4740" windowWidth="27640" windowHeight="16940" xr2:uid="{BC0DECDA-AED3-C249-929C-C34F56BC4720}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="66">
   <si>
     <t>Test Name</t>
   </si>
@@ -228,6 +228,12 @@
   </si>
   <si>
     <t>Behavioral monitoring and morphological analysis</t>
+  </si>
+  <si>
+    <t>Details</t>
+  </si>
+  <si>
+    <t>Behavioral</t>
   </si>
 </sst>
 </file>
@@ -623,15 +629,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228A0F75-F7E4-104E-B71B-3778F0496FB9}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.1640625" customWidth="1"/>
     <col min="2" max="2" width="65.1640625" customWidth="1"/>
     <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -644,8 +651,11 @@
       <c r="D1" s="3" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -653,13 +663,16 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -667,13 +680,16 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -681,13 +697,16 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -695,13 +714,16 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" t="s">
         <v>5</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -709,13 +731,16 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" t="s">
         <v>5</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -723,13 +748,16 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" t="s">
         <v>5</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -737,13 +765,16 @@
         <v>20</v>
       </c>
       <c r="C8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" t="s">
         <v>5</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -751,13 +782,16 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" t="s">
         <v>5</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -765,13 +799,16 @@
         <v>25</v>
       </c>
       <c r="C10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" t="s">
         <v>5</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>27</v>
       </c>
@@ -779,13 +816,16 @@
         <v>28</v>
       </c>
       <c r="C11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" t="s">
         <v>29</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>30</v>
       </c>
@@ -793,13 +833,16 @@
         <v>31</v>
       </c>
       <c r="C12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" t="s">
         <v>29</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>32</v>
       </c>
@@ -807,13 +850,16 @@
         <v>33</v>
       </c>
       <c r="C13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" t="s">
         <v>29</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>34</v>
       </c>
@@ -821,13 +867,16 @@
         <v>35</v>
       </c>
       <c r="C14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" t="s">
         <v>29</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>36</v>
       </c>
@@ -835,13 +884,16 @@
         <v>37</v>
       </c>
       <c r="C15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" t="s">
         <v>29</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>38</v>
       </c>
@@ -849,13 +901,16 @@
         <v>39</v>
       </c>
       <c r="C16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" t="s">
         <v>29</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>62</v>
       </c>
@@ -863,13 +918,16 @@
         <v>40</v>
       </c>
       <c r="C17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" t="s">
         <v>29</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>41</v>
       </c>
@@ -877,13 +935,16 @@
         <v>42</v>
       </c>
       <c r="C18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" t="s">
         <v>29</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>43</v>
       </c>
@@ -891,13 +952,16 @@
         <v>44</v>
       </c>
       <c r="C19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" t="s">
         <v>29</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>45</v>
       </c>
@@ -905,13 +969,16 @@
         <v>46</v>
       </c>
       <c r="C20" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" t="s">
         <v>29</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -919,13 +986,16 @@
         <v>48</v>
       </c>
       <c r="C21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" t="s">
         <v>63</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -933,13 +1003,16 @@
         <v>51</v>
       </c>
       <c r="C22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" t="s">
         <v>63</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -947,13 +1020,16 @@
         <v>54</v>
       </c>
       <c r="C23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" t="s">
         <v>63</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>56</v>
       </c>
@@ -961,9 +1037,12 @@
         <v>57</v>
       </c>
       <c r="C24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" t="s">
         <v>63</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>58</v>
       </c>
     </row>
